--- a/new-erp/NockERP-Staging-Test-2026-09-24.xlsx
+++ b/new-erp/NockERP-Staging-Test-2026-09-24.xlsx
@@ -11,9 +11,14 @@
     <sheet name="ผลเทสทั้งหมด" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ยังไม่ได้เทส" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="ข้อมูลเทสบน Staging" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Summary (EN)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="All Results (EN)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Not Tested (EN)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Test Data (EN)" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ผลเทสทั้งหมด'!$A$1:$J$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'All Results (EN)'!$A$1:$J$90</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5890,4 +5895,5350 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>NockERP Staging — Test Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Tester: Claude (Director + Teacher accounts) · All test data in TEST-Branch · 23–24 Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Fix first (Critical + High)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B5" s="5">
+        <f>COUNTA('All Results (EN)'!A2:A90)</f>
+        <v/>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>What was tested</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>✅ Pass</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>COUNTIF('All Results (EN)'!E2:E90,"✅ Pass")</f>
+        <v/>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>A8</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Edit class: change time/day</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Never modify Ended/Closed sessions or sessions with attendance</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="B7" s="5">
+        <f>COUNTIF('All Results (EN)'!E2:E90,"⚠️ Pass w/ notes")</f>
+        <v/>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Edit a single session (time)</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>"Just this session" must update the existing record, not create one · clean up existing duplicates</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>🔴 Bug</t>
+        </is>
+      </c>
+      <c r="B8" s="5">
+        <f>COUNTIF('All Results (EN)'!E2:E90,"🔴 Bug")</f>
+        <v/>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Attendance on a future session</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>Block attendance before the class date (except advance Leave, without changing session status)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>⬜ Not tested</t>
+        </is>
+      </c>
+      <c r="B9" s="5">
+        <f>COUNTIF('All Results (EN)'!E2:E90,"⬜ Not tested")</f>
+        <v/>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Remove student from class</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>Do it in one transaction: remove from class + future sessions · human-readable errors</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr"/>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Block Billing for Teachers in UI and API</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="B11" s="5">
+        <f>COUNTIF('All Results (EN)'!G2:G90,"🔧 Fix required")</f>
+        <v/>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Account auto-switch (Clerk multi-session)</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Disable Clerk multi-session or force a single active session</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>🔍 Needs verification</t>
+        </is>
+      </c>
+      <c r="B12" s="5">
+        <f>COUNTIF('All Results (EN)'!G2:G90,"🔍 Needs verification")</f>
+        <v/>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>A11</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Deactivate class</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>Confirm + cancel future sessions (or ask) + remove from Reschedule options</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>❓ Business rule decision</t>
+        </is>
+      </c>
+      <c r="B13" s="5">
+        <f>COUNTIF('All Results (EN)'!G2:G90,"❓ Business rule decision")</f>
+        <v/>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Single class over capacity</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Block when over capacity by class type (Single = 1, Group = 6) in UI and server</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr"/>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Rooms full (branch has 2 rooms) → 3rd class same time</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>Rooms full = block (or require override + reason)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Severity Critical</t>
+        </is>
+      </c>
+      <c r="B15" s="5">
+        <f>COUNTIF('All Results (EN)'!F2:F90,"Critical")</f>
+        <v/>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Status by time Upcoming→Live→Ended→Closed</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>Derive status from real time (Asia/Bangkok) · human-readable time format</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Severity High</t>
+        </is>
+      </c>
+      <c r="B16" s="5">
+        <f>COUNTIF('All Results (EN)'!F2:F90,"High")</f>
+        <v/>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>BL-14</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Maker–checker PDF approval</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>❓ Business rule decision</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>Define which roles may approve (suggest Admin/Manager/Director) and hide the button from others</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Severity Medium</t>
+        </is>
+      </c>
+      <c r="B17" s="5">
+        <f>COUNTIF('All Results (EN)'!F2:F90,"Medium")</f>
+        <v/>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>BL-17</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Refund / Credit note</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>❓ Business rule decision</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>Design a refund / credit note flow aligned with accounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Severity Low</t>
+        </is>
+      </c>
+      <c r="B18" s="5">
+        <f>COUNTIF('All Results (EN)'!F2:F90,"Low")</f>
+        <v/>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>BL-18</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Log payment (transfer + cash, partial)</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>❓ Business rule decision</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>Add maker–checker for payment confirmation (especially cash)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>BL-19</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Claim entitlement after full payment</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>🔍 Needs verification</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>Dev to confirm how the expiry date is calculated; it should end at the end of the paid month</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>BL-4</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Totals match everywhere (List / Drawer / Edit / PDF)</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>🔍 Needs verification</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>Dev to re-check 260922010010007 · confirm whether saving from Edit overwrites the PDF total</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Clear bug — Dev must fix</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>BL-5</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Negative "Periods purchased"</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>Enforce min = 1 in the input and on the server · inline error message</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>🔍 Needs verification</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Dev/owner must verify or retest</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>BL-6</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Bus fee ticked automatically</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>Default to unticked, or read bus usage from the student profile · warn before Generate if bus fee is included</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>❓ Business rule decision</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Not a pure bug — business rule must be decided first</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>BL-9</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Sequential invoice numbers</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>Reserve the number inside the same transaction that creates the invoice (rollback releases it), or assign at Approve</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Wrong data/money/permissions — not usable in production</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>First attendance click</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>One click always saves (auto-start class) + confirmation toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Affects daily operations</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Send to parent (no LINE)</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>Hide Send until Approved · confirm before sending · status "LINE not linked" instead of Sent</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Works but confusing/risky</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>E5</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Does Day view show every session?</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>Add a "No teacher" / "Unknown teacher" column in Day view · include removed teachers in the filter</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Minor UX</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Delete a teacher who still teaches active classes</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>Warn + require a replacement teacher first · display name of removed staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>F7</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Student status</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>Compute status/remaining sessions from real entitlements</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>❓ Business rule decision</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>Restrict Export to Admin and above</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>Disable sidebar link prefetch · cache reference data</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Director can delete themselves</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>Block self-delete / require at least one Director</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J90"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>What was tested</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="H1" s="14" t="inlineStr">
+        <is>
+          <t>Recommendation / Fix</t>
+        </is>
+      </c>
+      <c r="I1" s="14" t="inlineStr">
+        <is>
+          <t>Dev status</t>
+        </is>
+      </c>
+      <c r="J1" s="14" t="inlineStr">
+        <is>
+          <t>Dev notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>BL-1</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Generate PDF (previously stuck on "Generating…" forever in TEST-Branch)</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Fixed: stuck invoices recover via Retry PDF in the table (~20 s) · new invoices generate in ~30 s · the retry icon in the drawer does nothing · no toast when the PDF is ready</t>
+        </is>
+      </c>
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F2" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Make the drawer icon work like the table button + add a tooltip · toast on PDF ready/failed · add a timeout that switches to "Failed – Retry" instead of spinning forever</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr"/>
+      <c r="J2" s="8" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>BL-2</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Course period + monthly pro-rate (2 months from 29 Sep)</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Fixed: 29 Sep → 31 Oct · Sep 30% ฿1,350 + Oct 100% ฿4,500 correct · but the summary line says "5 sessions · 10 hrs" while it is really 4 × 1 hr (counts the holiday and doubles hours) · header says "→27 Oct" but footer says "→31 Oct"</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>🔴 Bug</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>Count sessions/hours from the sessions actually generated (excluding holidays) and sum real session durations · reuse the same function used for price and bus fee</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr"/>
+      <c r="J3" s="8" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>BL-3</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Create vs Edit numbers for the same invoice</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Create shows Oct "Max 3 sessions" · Edit of the same invoice shows "Max 4 sessions" (price identical)</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>🔴 Bug</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>Create and Edit must share one calculation (one of them is not skipping holidays)</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr"/>
+      <c r="J4" s="8" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>BL-4</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Totals match everywhere (List / Drawer / Edit / PDF)</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>New invoice 260924010020006 matches everywhere (฿6,900) · old invoice 260922010010007 (Thong lo) where PDF ≠ Edit not re-checked</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>🔍 Needs verification</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>Dev to re-check 260922010010007 · confirm whether saving from Edit overwrites the PDF total</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>BL-5</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Negative "Periods purchased"</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Entering -1 → price ฿-4,500 (not fixed)</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>🔴 Bug</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>Enforce min = 1 in the input and on the server · inline error message</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr"/>
+      <c r="J6" s="8" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>BL-6</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Bus fee ticked automatically</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Pickup + Drop off pre-ticked for every ride (฿1,200) even if the student may not use the bus (not fixed) · unticking individual legs recalculates correctly</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>🔴 Bug</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>Default to unticked, or read bus usage from the student profile · warn before Generate if bus fee is included</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr"/>
+      <c r="J7" s="8" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>BL-7</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Void invoice without a reason</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Toast "Enter a reason for voiding this invoice" appears (no longer silent) · Reason field has no * and the button is not disabled · text "…0006will" missing a space</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>Mark Reason as required (*) + disable the button until filled · fix the missing space</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr"/>
+      <c r="J8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>BL-8</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Save draft (new feature)</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Saves + toast + list refreshes immediately · draft gets a real invoice number right away (260924010020006) · timeline ticks "Invoice Created" ✓ while still a draft</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>❓ Business rule decision</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>Assign the invoice number at Generate/Approve instead of Save draft so deleted drafts leave no gaps · show "Draft" in the timeline</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr"/>
+      <c r="J9" s="8" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>BL-9</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Sequential invoice numbers</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Number jumped 0003 → 0005 (0004 lost when the server returned 500) · tax invoices should be sequential</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>🔴 Bug</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Reserve the number inside the same transaction that creates the invoice (rollback releases it), or assign at Approve</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr"/>
+      <c r="J10" s="8" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>BL-10</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Summary cards (Revenue/Pending/Cancel/Total)</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>PENDING card = 0 while 3 invoices await approval (header says "3 pending approvals") → "Pending" means two different things</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>Rename cards clearly, e.g. "Awaiting payment" vs "Awaiting PDF approval", or add an approval card</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr"/>
+      <c r="J11" s="8" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>BL-11</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Filters Draft/Pending/Paid/Void + date range</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Filter correctly</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>✅ Pass</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr"/>
+      <c r="I12" s="8" t="inlineStr"/>
+      <c r="J12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>BL-12</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Choosing a class when creating an invoice</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>One-off classes (Test/Exam) offered for a 2-month course · class of a deleted teacher still selectable, and the invoice links to the deleted teacher</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>Show only active Learning classes with active teachers · warn if the class teacher was removed</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr"/>
+      <c r="J13" s="8" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>BL-13</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Invoice detail drawer</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Family shows "—" while the list shows "Family Family" · course shows "1m" although 2 months were bought</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>Load family consistently with the list · show the number of months actually purchased</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr"/>
+      <c r="J14" s="8" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>BL-14</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Maker–checker PDF approval</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Creator cannot approve own invoice ✅ · but a Teacher (Dai Breezy) can approve invoices</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>🔴 Bug</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>❓ Business rule decision</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>Define which roles may approve (suggest Admin/Manager/Director) and hide the button from others</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr"/>
+      <c r="J15" s="8" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>BL-15</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Send to Parent without LINE</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Toast "nothing was delivered" + Send again ✅ · but the timeline ticks ✓ on Send although nothing reached the parent</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>Separate status "Not delivered / LINE not linked" instead of a ✓</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr"/>
+      <c r="J16" s="8" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>BL-16</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Send button in the table when Note to parent is empty</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Last time nothing visible happened (a fast-disappearing toast is possible)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>⬜ Not tested</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>🔍 Needs verification</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>Retest: if no toast, show a warning or open the drawer at the Note field</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr"/>
+      <c r="J17" s="8" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>BL-17</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Refund / Credit note</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Not available · Void is blocked once paid (correct) but there is no way to refund</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>❓ Business rule decision</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>Design a refund / credit note flow aligned with accounting</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr"/>
+      <c r="J18" s="8" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>BL-18</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Log payment (transfer + cash, partial)</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Partial payment works + overpayment blocked ✅ · the same person can record and confirm the money</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>❓ Business rule decision</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>Add maker–checker for payment confirmation (especially cash)</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr"/>
+      <c r="J19" s="8" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>BL-19</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Claim entitlement after full payment</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Auto-claim ✅ · paid Sep pro-rate 30% but entitlement "Renews 23 Oct" → may get more classes than paid for</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>🔍 Needs verification</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>Dev to confirm how the expiry date is calculated; it should end at the end of the paid month</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr"/>
+      <c r="J20" s="8" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>BL-20</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Receipt</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Created (Split receipt available) ✅ · drawer does not refresh after creation (risk of double-click) · receipt number uses the same format as invoice numbers</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>Refresh drawer + prevent double submit · use a separate prefix, e.g. RC-…</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr"/>
+      <c r="J21" s="8" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>BL-21</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Bank reconciliation</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Transaction id → ready to send to accountant ✅ · reference entered when uploading the slip is not reused</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>Prefill the reference from the slip</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr"/>
+      <c r="J22" s="8" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>BL-22</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Branch brand Nockacademy but bank account is Liclass</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Bank account auto-linked, not editable on the branch page</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F23" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>🔍 Needs verification</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>Review brand ↔ bank account mapping; make it editable per branch</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr"/>
+      <c r="J23" s="8" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>BL-23</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Billing screen at ~1200px width</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Table overflows horizontally; Ref # column is cut off</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>Scroll inside the table container or hide secondary columns on narrow screens</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr"/>
+      <c r="J24" s="8" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Create a single-day Learning class → 8 weeks, skip holiday</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>7 sessions (13 Oct skipped)</t>
+        </is>
+      </c>
+      <c r="E25" s="19" t="inlineStr">
+        <is>
+          <t>✅ Pass</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr"/>
+      <c r="I25" s="8" t="inlineStr"/>
+      <c r="J25" s="8" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Select multiple days / Add another day</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Wed+Thu+Fri → 3 separate classes · class starting today generates 9 sessions (incl. today)</t>
+        </is>
+      </c>
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>✅ Pass</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr"/>
+      <c r="I26" s="8" t="inlineStr"/>
+      <c r="J26" s="8" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Different teacher per row</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Works · teacher not teaching the subject forces Remarks (good) but does not say which row · Create button disabled without explanation</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>Point to the problem row + tooltip explaining why the button is disabled</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr"/>
+      <c r="J27" s="8" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Single class over capacity</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>A Single class accepts 2 students · text still says "max 6" · class grade becomes P.1, P.5</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="inlineStr">
+        <is>
+          <t>🔴 Bug</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>Block when over capacity by class type (Single = 1, Group = 6) in UI and server</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr"/>
+      <c r="J28" s="8" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Rooms full (branch has 2 rooms) → 3rd class same time</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Shows "all 2 room(s) booked" but still creates the 3rd class (Fri 25 Sep 11:00 has 3 classes)</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>🔴 Bug</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>Rooms full = block (or require override + reason)</t>
+        </is>
+      </c>
+      <c r="I29" s="8" t="inlineStr"/>
+      <c r="J29" s="8" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Teacher time clash</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Blocked ✅ · need to retest whether a toast appears</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>🔍 Needs verification</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>Retest toast</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="inlineStr"/>
+      <c r="J30" s="8" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Create class on a day the branch is closed</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Warns but allows · time picker fixed to 09–20, not the branch opening hours</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F31" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>❓ Business rule decision</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>Decide block vs warn · use real branch opening hours</t>
+        </is>
+      </c>
+      <c r="I31" s="8" t="inlineStr"/>
+      <c r="J31" s="8" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>A8</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Edit class: change time/day</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Future sessions change correctly, but today's ended session (with attendance + summary) also moved 16:00→18:00 = rewrites history</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>🔴 Bug</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>Never modify Ended/Closed sessions or sessions with attendance</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="inlineStr"/>
+      <c r="J32" s="8" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>A9</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Edit class: change teacher</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Asks "Update sessions?" ✅ · customized sessions keep teacher ✅ · Calendar shows the teacher as a UUID</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>🔴 Bug</t>
+        </is>
+      </c>
+      <c r="F33" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>Display the name from the staff table (removed staff → "Name (left)")</t>
+        </is>
+      </c>
+      <c r="I33" s="8" t="inlineStr"/>
+      <c r="J33" s="8" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Add a holiday after the class exists</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>Session stays with a Holiday badge · students still booked · no warning / notification</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F34" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>❓ Business rule decision</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>When adding a holiday list affected sessions + let admin cancel/move + notify parents</t>
+        </is>
+      </c>
+      <c r="I34" s="8" t="inlineStr"/>
+      <c r="J34" s="8" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>A11</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Deactivate class</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>No confirm · future sessions remain Upcoming · still offered as a Reschedule target</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="inlineStr">
+        <is>
+          <t>🔴 Bug</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>Confirm + cancel future sessions (or ask) + remove from Reschedule options</t>
+        </is>
+      </c>
+      <c r="I35" s="8" t="inlineStr"/>
+      <c r="J35" s="8" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>A12</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Class for = Test/Interview (one-off)</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>Creates 1 session ✅ · displayed like a weekly class ("Fri · 11:00") and counted as Recurring</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F36" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>Show the full date + do not count as recurring</t>
+        </is>
+      </c>
+      <c r="I36" s="8" t="inlineStr"/>
+      <c r="J36" s="8" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>A13</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>Add sessions from the class Sessions tab</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>+2 → appended 19, 26 Nov + toast</t>
+        </is>
+      </c>
+      <c r="E37" s="19" t="inlineStr">
+        <is>
+          <t>✅ Pass</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr"/>
+      <c r="I37" s="8" t="inlineStr"/>
+      <c r="J37" s="8" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Session</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Add session attached to a class</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>Does not pull the class students (0 students)</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F38" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>Default to the class roster</t>
+        </is>
+      </c>
+      <c r="I38" s="8" t="inlineStr"/>
+      <c r="J38" s="8" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Session</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Standalone / Trial session</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Created with Trial badge · attendance + summary work · can be created outside opening hours (warning only)</t>
+        </is>
+      </c>
+      <c r="E39" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F39" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>❓ Business rule decision</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>Decide block vs warn outside opening hours</t>
+        </is>
+      </c>
+      <c r="I39" s="8" t="inlineStr"/>
+      <c r="J39" s="8" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Session</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Edit a single session (time)</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>"Just this session" creates a duplicate (1 Oct has both 16:00 original + 17:00 new) · confirmation text shows the wrong new time</t>
+        </is>
+      </c>
+      <c r="E40" s="17" t="inlineStr">
+        <is>
+          <t>🔴 Bug</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>"Just this session" must update the existing record, not create one · clean up existing duplicates</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="inlineStr"/>
+      <c r="J40" s="8" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Session</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>Delete session with students</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Notification sent ✅ · dialog does not say how many students</t>
+        </is>
+      </c>
+      <c r="E41" s="19" t="inlineStr">
+        <is>
+          <t>✅ Pass</t>
+        </is>
+      </c>
+      <c r="F41" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>(Nice to have) show student count in the dialog</t>
+        </is>
+      </c>
+      <c r="I41" s="8" t="inlineStr"/>
+      <c r="J41" s="8" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Session</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>Status by time Upcoming→Live→Ended→Closed</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>Does not follow the clock · stuck Live for hours after attendance · raw ISO UTC time shown</t>
+        </is>
+      </c>
+      <c r="E42" s="17" t="inlineStr">
+        <is>
+          <t>🔴 Bug</t>
+        </is>
+      </c>
+      <c r="F42" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>Derive status from real time (Asia/Bangkok) · human-readable time format</t>
+        </is>
+      </c>
+      <c r="I42" s="8" t="inlineStr"/>
+      <c r="J42" s="8" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Session</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Closed status</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Auto-closes overnight + locks attendance ✅ · "start 15:52 · end 09:00" has no dates</t>
+        </is>
+      </c>
+      <c r="E43" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F43" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>Show dates with times</t>
+        </is>
+      </c>
+      <c r="I43" s="8" t="inlineStr"/>
+      <c r="J43" s="8" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>First attendance click</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>Outside class time: first click = Start class (not saved), must click again · no toast</t>
+        </is>
+      </c>
+      <c r="E44" s="17" t="inlineStr">
+        <is>
+          <t>🔴 Bug</t>
+        </is>
+      </c>
+      <c r="F44" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>One click always saves (auto-start class) + confirmation toast</t>
+        </is>
+      </c>
+      <c r="I44" s="8" t="inlineStr"/>
+      <c r="J44" s="8" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>Attendance on a future session</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Allowed + session status breaks (future becomes Ended/Live)</t>
+        </is>
+      </c>
+      <c r="E45" s="17" t="inlineStr">
+        <is>
+          <t>🔴 Bug</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>Block attendance before the class date (except advance Leave, without changing session status)</t>
+        </is>
+      </c>
+      <c r="I45" s="8" t="inlineStr"/>
+      <c r="J45" s="8" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>Change Present ↔ Absent ↔ Leave</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Works · summary deleted when switching to Absent · cannot reset to "not marked"</t>
+        </is>
+      </c>
+      <c r="E46" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F46" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>Add Undo/Clear · warn before deleting a summary</t>
+        </is>
+      </c>
+      <c r="I46" s="8" t="inlineStr"/>
+      <c r="J46" s="8" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>Session-count student: Present deducts</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>Deducts correctly 3→2 ✅ · Add Student sessions field defaults to 0 · three pages show different numbers (1/8, 0/3, 2 left)</t>
+        </is>
+      </c>
+      <c r="E47" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F47" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>Default from the purchased package · consistent wording/numbers everywhere</t>
+        </is>
+      </c>
+      <c r="I47" s="8" t="inlineStr"/>
+      <c r="J47" s="8" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>Leave over quota</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>3-session pack = 0 leave quota · formula unknown</t>
+        </is>
+      </c>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F48" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>❓ Business rule decision</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>Dev to confirm the leave quota formula + show remaining quota</t>
+        </is>
+      </c>
+      <c r="I48" s="8" t="inlineStr"/>
+      <c r="J48" s="8" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>No sessions left → button locked</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>"No sessions remaining"</t>
+        </is>
+      </c>
+      <c r="E49" s="19" t="inlineStr">
+        <is>
+          <t>✅ Pass</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="inlineStr"/>
+      <c r="I49" s="8" t="inlineStr"/>
+      <c r="J49" s="8" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>Reschedule into another session</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>Moves correctly ✅ · can move into a session of a deactivated class · source still counts 2 students · Attendance page = coming soon</t>
+        </is>
+      </c>
+      <c r="E50" s="17" t="inlineStr">
+        <is>
+          <t>🔴 Bug</t>
+        </is>
+      </c>
+      <c r="F50" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>Exclude inactive classes · update source count · enable Reschedule on the Attendance page</t>
+        </is>
+      </c>
+      <c r="I50" s="8" t="inlineStr"/>
+      <c r="J50" s="8" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>Summary cards by date range</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>Not filtered by range (counts items outside the week)</t>
+        </is>
+      </c>
+      <c r="E51" s="17" t="inlineStr">
+        <is>
+          <t>🔴 Bug</t>
+        </is>
+      </c>
+      <c r="F51" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>Query by the selected date range</t>
+        </is>
+      </c>
+      <c r="I51" s="8" t="inlineStr"/>
+      <c r="J51" s="8" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>Subject filter</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>Mock data, not real subjects</t>
+        </is>
+      </c>
+      <c r="E52" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F52" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>Load subjects from the branch</t>
+        </is>
+      </c>
+      <c r="I52" s="8" t="inlineStr"/>
+      <c r="J52" s="8" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>Summary slot only for Present students</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E53" s="19" t="inlineStr">
+        <is>
+          <t>✅ Pass</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H53" s="8" t="inlineStr"/>
+      <c r="I53" s="8" t="inlineStr"/>
+      <c r="J53" s="8" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>Save Draft → Submit → Approve</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E54" s="19" t="inlineStr">
+        <is>
+          <t>✅ Pass</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H54" s="8" t="inlineStr"/>
+      <c r="I54" s="8" t="inlineStr"/>
+      <c r="J54" s="8" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>Request changes → edit → resubmit</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E55" s="19" t="inlineStr">
+        <is>
+          <t>✅ Pass</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H55" s="8" t="inlineStr"/>
+      <c r="I55" s="8" t="inlineStr"/>
+      <c r="J55" s="8" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>Edit a summary after Approve</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>Text is read-only; must Request changes → edit → Resubmit → Approve · Director can do the whole loop alone (edit on behalf of teacher + self-approve), no record of who edited</t>
+        </is>
+      </c>
+      <c r="E56" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F56" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G56" s="8" t="inlineStr">
+        <is>
+          <t>❓ Business rule decision</t>
+        </is>
+      </c>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>Keep edit history · editor cannot approve own change · editing after Sent not yet tested</t>
+        </is>
+      </c>
+      <c r="I56" s="8" t="inlineStr"/>
+      <c r="J56" s="8" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>Send to parent (no LINE)</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>Can send while still "Awaiting approval" (skips approval) · no confirm · shows Sent although no LINE</t>
+        </is>
+      </c>
+      <c r="E57" s="17" t="inlineStr">
+        <is>
+          <t>🔴 Bug</t>
+        </is>
+      </c>
+      <c r="F57" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>Hide Send until Approved · confirm before sending · status "LINE not linked" instead of Sent</t>
+        </is>
+      </c>
+      <c r="I57" s="8" t="inlineStr"/>
+      <c r="J57" s="8" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>"Not written yet" counter / summary cards</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>Cards not filtered by date range · same item shows both Sent and Parent not linked</t>
+        </is>
+      </c>
+      <c r="E58" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F58" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>Filter by range · make statuses consistent</t>
+        </is>
+      </c>
+      <c r="I58" s="8" t="inlineStr"/>
+      <c r="J58" s="8" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>Teacher writes → Director approves</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>Works on both sides + correct toast · Send button shows "Sending…" while Approve runs (misleading) · Director can edit teacher text before approving · session shows "start 09:07 · end 09:07"</t>
+        </is>
+      </c>
+      <c r="E59" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F59" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>Loading state only on the clicked button · record real start/end times</t>
+        </is>
+      </c>
+      <c r="I59" s="8" t="inlineStr"/>
+      <c r="J59" s="8" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>D8</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>Approve own summary</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t>Writer can approve own summary (invoices forbid this)</t>
+        </is>
+      </c>
+      <c r="E60" s="17" t="inlineStr">
+        <is>
+          <t>🔴 Bug</t>
+        </is>
+      </c>
+      <c r="F60" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G60" s="8" t="inlineStr">
+        <is>
+          <t>❓ Business rule decision</t>
+        </is>
+      </c>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>Apply the same maker–checker rule as invoices, or confirm it is allowed</t>
+        </is>
+      </c>
+      <c r="I60" s="8" t="inlineStr"/>
+      <c r="J60" s="8" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>Calendar</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>Sessions shown in every view</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>Week/Month/List show all (see E5 for Day)</t>
+        </is>
+      </c>
+      <c r="E61" s="19" t="inlineStr">
+        <is>
+          <t>✅ Pass</t>
+        </is>
+      </c>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H61" s="8" t="inlineStr"/>
+      <c r="I61" s="8" t="inlineStr"/>
+      <c r="J61" s="8" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>Calendar</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>Reflects edit/delete/reschedule</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>Keeps up, but reflects bug B3 + teacher UUID · class page list does not refresh</t>
+        </is>
+      </c>
+      <c r="E62" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F62" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G62" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>Fix root causes B3/A9 · refresh list after edits</t>
+        </is>
+      </c>
+      <c r="I62" s="8" t="inlineStr"/>
+      <c r="J62" s="8" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>Calendar</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>Create Class from an empty slot</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>Prefills branch/teacher/date/time correctly + toast "Class created" + appears in Calendar ✅ · defaults to 2 hrs · no room assigned · card shows only the subject</t>
+        </is>
+      </c>
+      <c r="E63" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F63" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G63" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>Default to the branch standard duration · auto-pick a free room · show class name on the card</t>
+        </is>
+      </c>
+      <c r="I63" s="8" t="inlineStr"/>
+      <c r="J63" s="8" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>Calendar</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>Summary → Export PDF</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>Title says "Week" but the table lists 18 sessions from 23 Sep–14 Oct · the 3 clashing sessions show "OK" (only holidays checked) · Export PDF not clicked (download needs permission)</t>
+        </is>
+      </c>
+      <c r="E64" s="17" t="inlineStr">
+        <is>
+          <t>🔴 Bug</t>
+        </is>
+      </c>
+      <c r="F64" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G64" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H64" s="8" t="inlineStr">
+        <is>
+          <t>Filter to the visible range · detect room/teacher clashes and show Conflict · (pending) test Export PDF</t>
+        </is>
+      </c>
+      <c r="I64" s="8" t="inlineStr"/>
+      <c r="J64" s="8" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>E5</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>Calendar</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>Does Day view show every session?</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>Hides sessions with no teacher / removed teacher: today 16:00 missing · 25 Sep Month says ×5 but Day shows 2 · "No teacher" filter in Day = empty · UUID teacher not in dropdown → a slot that looks free may not be, creating a class there clashes silently</t>
+        </is>
+      </c>
+      <c r="E65" s="17" t="inlineStr">
+        <is>
+          <t>🔴 Bug</t>
+        </is>
+      </c>
+      <c r="F65" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G65" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>Add a "No teacher" / "Unknown teacher" column in Day view · include removed teachers in the filter</t>
+        </is>
+      </c>
+      <c r="I65" s="8" t="inlineStr"/>
+      <c r="J65" s="8" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>E6</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>Calendar</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>Week view</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>Shows everything ✅ · clashing sessions squeezed until unreadable · label "Week 4" unclear</t>
+        </is>
+      </c>
+      <c r="E66" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F66" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G66" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>Show "+2 more" and expand on click · label as a date range, e.g. 21–27 Sep</t>
+        </is>
+      </c>
+      <c r="I66" s="8" t="inlineStr"/>
+      <c r="J66" s="8" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>E7</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>Calendar</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>Month view</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>Groups "Maths ×N" + red conflict dot + holiday highlight ✅ · weeks start Sunday while Week view starts Monday · hover popover appears in the wrong place</t>
+        </is>
+      </c>
+      <c r="E67" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F67" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G67" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>Use the same week start · fix popover position</t>
+        </is>
+      </c>
+      <c r="I67" s="8" t="inlineStr"/>
+      <c r="J67" s="8" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>Cross-module</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>Remove student from class</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>"An unexpected error occurred" → raw error with UUIDs → class ends up empty but future sessions still have the student</t>
+        </is>
+      </c>
+      <c r="E68" s="17" t="inlineStr">
+        <is>
+          <t>🔴 Bug</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G68" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>Do it in one transaction: remove from class + future sessions · human-readable errors</t>
+        </is>
+      </c>
+      <c r="I68" s="8" t="inlineStr"/>
+      <c r="J68" s="8" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>Cross-module</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>Delete a teacher who still teaches active classes</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>Deleted without warning → other pages show a UUID instead of the name</t>
+        </is>
+      </c>
+      <c r="E69" s="17" t="inlineStr">
+        <is>
+          <t>🔴 Bug</t>
+        </is>
+      </c>
+      <c r="F69" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G69" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>Warn + require a replacement teacher first · display name of removed staff</t>
+        </is>
+      </c>
+      <c r="I69" s="8" t="inlineStr"/>
+      <c r="J69" s="8" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>Cross-module</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>Claim from invoice → student joins class</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t>Auto-claim ✅</t>
+        </is>
+      </c>
+      <c r="E70" s="19" t="inlineStr">
+        <is>
+          <t>✅ Pass</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="8" t="inlineStr"/>
+      <c r="I70" s="8" t="inlineStr"/>
+      <c r="J70" s="8" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>Cross-module</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>Low-sessions notification</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>Now exists (Urgent "1 session left" / "0 sessions left" + Send LINE reminder button) · StudentA is on a subscription but counted as "1 session left" · typing /billing in the URL redirects to Notifications</t>
+        </is>
+      </c>
+      <c r="E71" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F71" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>Do not send session-count alerts for subscription students · fix routing</t>
+        </is>
+      </c>
+      <c r="I71" s="8" t="inlineStr"/>
+      <c r="J71" s="8" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>Cross-module</t>
+        </is>
+      </c>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>Student profile matches sessions</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t>Attendance matches ✅ · session page does not show Leave</t>
+        </is>
+      </c>
+      <c r="E72" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F72" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G72" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H72" s="8" t="inlineStr">
+        <is>
+          <t>Show leave status on the session page</t>
+        </is>
+      </c>
+      <c r="I72" s="8" t="inlineStr"/>
+      <c r="J72" s="8" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>F6</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>Cross-module</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>Teacher names inconsistent across pages</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>Billing = "Dai Breezy"/"NockAcademy LMS" · Calendar = "dai Test"/UUID</t>
+        </is>
+      </c>
+      <c r="E73" s="17" t="inlineStr">
+        <is>
+          <t>🔴 Bug</t>
+        </is>
+      </c>
+      <c r="F73" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>Use a single source for display names</t>
+        </is>
+      </c>
+      <c r="I73" s="8" t="inlineStr"/>
+      <c r="J73" s="8" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>F7</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>Cross-module</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>Student status</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t>Student in 4 classes but Inactive · Classes Left 0 although subscription paid</t>
+        </is>
+      </c>
+      <c r="E74" s="17" t="inlineStr">
+        <is>
+          <t>🔴 Bug</t>
+        </is>
+      </c>
+      <c r="F74" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G74" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>Compute status/remaining sessions from real entitlements</t>
+        </is>
+      </c>
+      <c r="I74" s="8" t="inlineStr"/>
+      <c r="J74" s="8" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>F8</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>Cross-module</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>Student grade vs course/class grade</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>P.1 student can buy a P.5 course and join a P.5 class without warning</t>
+        </is>
+      </c>
+      <c r="E75" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F75" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>❓ Business rule decision</t>
+        </is>
+      </c>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>Warn (or block) on grade mismatch</t>
+        </is>
+      </c>
+      <c r="I75" s="8" t="inlineStr"/>
+      <c r="J75" s="8" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>Teacher role</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>Sidebar</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>Sees every menu like a Director</t>
+        </is>
+      </c>
+      <c r="E76" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F76" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G76" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H76" s="8" t="inlineStr">
+        <is>
+          <t>Hide menus the role cannot use</t>
+        </is>
+      </c>
+      <c r="I76" s="8" t="inlineStr"/>
+      <c r="J76" s="8" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>Teacher role</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>Full access: sees revenue, New Invoice, Send to accountant, Approve invoice</t>
+        </is>
+      </c>
+      <c r="E77" s="17" t="inlineStr">
+        <is>
+          <t>🔴 Bug</t>
+        </is>
+      </c>
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H77" s="8" t="inlineStr">
+        <is>
+          <t>Block Billing for Teachers in UI and API</t>
+        </is>
+      </c>
+      <c r="I77" s="8" t="inlineStr"/>
+      <c r="J77" s="8" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>Teacher role</t>
+        </is>
+      </c>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>Can export student data (PII) + Add Student</t>
+        </is>
+      </c>
+      <c r="E78" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F78" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G78" s="8" t="inlineStr">
+        <is>
+          <t>❓ Business rule decision</t>
+        </is>
+      </c>
+      <c r="H78" s="8" t="inlineStr">
+        <is>
+          <t>Restrict Export to Admin and above</t>
+        </is>
+      </c>
+      <c r="I78" s="8" t="inlineStr"/>
+      <c r="J78" s="8" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>G4</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>Teacher role</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>Classes/Sessions</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>Can create classes · assign other teachers · see every teacher's sessions</t>
+        </is>
+      </c>
+      <c r="E79" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F79" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t>❓ Business rule decision</t>
+        </is>
+      </c>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>Confirm the intended teacher scope</t>
+        </is>
+      </c>
+      <c r="I79" s="8" t="inlineStr"/>
+      <c r="J79" s="8" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>Teacher role</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>Staff/Settings/Courses/Summary</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>Read-only / no create buttons / can Submit but not Approve</t>
+        </is>
+      </c>
+      <c r="E80" s="19" t="inlineStr">
+        <is>
+          <t>✅ Pass</t>
+        </is>
+      </c>
+      <c r="F80" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="8" t="inlineStr"/>
+      <c r="I80" s="8" t="inlineStr"/>
+      <c r="J80" s="8" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>Teacher role</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t>Account auto-switch (Clerk multi-session)</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>If a Director session exists in the same browser, a Teacher opening /billing is switched to Director automatically</t>
+        </is>
+      </c>
+      <c r="E81" s="17" t="inlineStr">
+        <is>
+          <t>🔴 Bug</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G81" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>Disable Clerk multi-session or force a single active session</t>
+        </is>
+      </c>
+      <c r="I81" s="8" t="inlineStr"/>
+      <c r="J81" s="8" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>TTFB 2–3 s · data appears after 8–9 s · every navigation prefetches all menus again (&gt;2,700 requests)</t>
+        </is>
+      </c>
+      <c r="E82" s="17" t="inlineStr">
+        <is>
+          <t>🔴 Bug</t>
+        </is>
+      </c>
+      <c r="F82" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G82" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H82" s="8" t="inlineStr">
+        <is>
+          <t>Disable sidebar link prefetch · cache reference data</t>
+        </is>
+      </c>
+      <c r="I82" s="8" t="inlineStr"/>
+      <c r="J82" s="8" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>Malformed URL id</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>Server crash instead of 404 · 404 page has no sidebar</t>
+        </is>
+      </c>
+      <c r="E83" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F83" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G83" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H83" s="8" t="inlineStr">
+        <is>
+          <t>Validate ids → 404 inside the app layout</t>
+        </is>
+      </c>
+      <c r="I83" s="8" t="inlineStr"/>
+      <c r="J83" s="8" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>Switch branch</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>Current page does not update, needs a reload</t>
+        </is>
+      </c>
+      <c r="E84" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F84" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G84" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>Refetch on branch change</t>
+        </is>
+      </c>
+      <c r="I84" s="8" t="inlineStr"/>
+      <c r="J84" s="8" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>Family form validation</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>Phone "abc", postcode "abcde", birth year 2030 all accepted</t>
+        </is>
+      </c>
+      <c r="E85" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F85" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H85" s="8" t="inlineStr">
+        <is>
+          <t>Validate formats</t>
+        </is>
+      </c>
+      <c r="I85" s="8" t="inlineStr"/>
+      <c r="J85" s="8" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t>No-login staff</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t>Email still required</t>
+        </is>
+      </c>
+      <c r="E86" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F86" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G86" s="8" t="inlineStr">
+        <is>
+          <t>❓ Business rule decision</t>
+        </is>
+      </c>
+      <c r="H86" s="8" t="inlineStr">
+        <is>
+          <t>Allow empty email</t>
+        </is>
+      </c>
+      <c r="I86" s="8" t="inlineStr"/>
+      <c r="J86" s="8" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>Director can delete themselves</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>Delete button on own account (not clicked)</t>
+        </is>
+      </c>
+      <c r="E87" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F87" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H87" s="8" t="inlineStr">
+        <is>
+          <t>Block self-delete / require at least one Director</t>
+        </is>
+      </c>
+      <c r="I87" s="8" t="inlineStr"/>
+      <c r="J87" s="8" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="8" t="inlineStr">
+        <is>
+          <t>S7</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t>Clerk development keys</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t>Used on staging</t>
+        </is>
+      </c>
+      <c r="E88" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F88" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G88" s="8" t="inlineStr">
+        <is>
+          <t>🔍 Needs verification</t>
+        </is>
+      </c>
+      <c r="H88" s="8" t="inlineStr">
+        <is>
+          <t>Switch to production keys before go-live</t>
+        </is>
+      </c>
+      <c r="I88" s="8" t="inlineStr"/>
+      <c r="J88" s="8" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t>Unfinished / leaking UX</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>Smart search / Message / Call buttons do nothing · tooltips leak dev notes ("(D3)", "Step 7") · raw Zod errors · fake badge counts on CRM/Inbox</t>
+        </is>
+      </c>
+      <c r="E89" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F89" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G89" s="8" t="inlineStr">
+        <is>
+          <t>🔧 Fix required</t>
+        </is>
+      </c>
+      <c r="H89" s="8" t="inlineStr">
+        <is>
+          <t>Hide unfinished features · rewrite messages</t>
+        </is>
+      </c>
+      <c r="I89" s="8" t="inlineStr"/>
+      <c r="J89" s="8" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>S9</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C90" s="8" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t>Unusable (sidebar takes 60%, no hamburger)</t>
+        </is>
+      </c>
+      <c r="E90" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Pass w/ notes</t>
+        </is>
+      </c>
+      <c r="F90" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G90" s="8" t="inlineStr">
+        <is>
+          <t>❓ Business rule decision</t>
+        </is>
+      </c>
+      <c r="H90" s="8" t="inlineStr">
+        <is>
+          <t>Decide whether mobile is required (teachers will likely take attendance on phones)</t>
+        </is>
+      </c>
+      <c r="I90" s="8" t="inlineStr"/>
+      <c r="J90" s="8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J90"/>
+  <dataValidations count="1">
+    <dataValidation sqref="I2:I90" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Not started,In progress,Fixed - retest,Passed,Won't fix"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>Not yet tested</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>Reason / what is needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Export PDF from Calendar Summary</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Downloads a file — waiting for owner permission</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Group class accepting a 7th student</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Only 2 test students exist</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Toast on teacher time clash</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Needs retest (toasts vanish in ~4 s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>BL-16</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Send button in table without Note to parent</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Needs retest</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Editing a summary already sent to the parent</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Requires a real send (not allowed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>BL-4</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Totals of invoice 260922010010007 (Thong lo)</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Dev data — Dev to check</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>LINE: real sending of invoice/receipt/summary, parent link code</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Requires a staging LINE OA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Send to accountant (email batch)</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Not allowed to click</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Admin / Manager / Area Manager permissions</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Requires an account per role</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Forgot password / sign up</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Not tested yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Switch language to Thai</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Not tested yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Renew flow / Deactivate branch</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Not tested yet</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>Items</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>TEST-Branch</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Packages / Fees / Promo / Holiday</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Maths P.5/P.6 · Bus TEST-Standard ฿150 · TEST-Entry ฿500 · TEST-Promo −10% · TEST-Holiday 13 Oct</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Staff</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>TEST-Teacher (deleted) · Dai Breezy (shown as "dai Test") used as the Teacher account</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Course</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>TEST-Course Maths P5 ฿4,500/month</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Maths Tue 10:00 · TEST-Count · TEST-Exam · TEST-Room2 · TEST-Room3 · TEST-E3 Calendar (Fri 25 Sep 14:00)</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Family / Students</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Family Family · TEST-StudentA (P.5) · TEST-StudentB (P.1)</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Invoices</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>260923020020001 Void · 260923010020002 / 0003 awaiting approval · 260923010020005 Paid · 260924010020006 awaiting approval</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Sessions / Summary</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Trial 24 Sep 09:00 (summary Approved, not sent) · 29 Sep Present · 6 Oct Leave</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Thong lo data untouched · Send to accountant never clicked · no real LINE messages sent · delete/deactivate this data after Dev review</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>